--- a/outputs/daily/hr_rankings_2026-10-04_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-04_full.xlsx
@@ -1066,34 +1066,30 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1350,34 +1346,30 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1874,34 +1866,30 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2158,34 +2146,30 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2442,34 +2426,30 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2726,34 +2706,30 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3010,34 +2986,30 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3294,34 +3266,30 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3818,34 +3786,30 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4102,34 +4066,30 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5934,34 +5894,30 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -6458,34 +6414,30 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6982,34 +6934,30 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7818,34 +7766,30 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 9 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8340,28 +8284,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y30" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8616,28 +8564,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y31" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8892,28 +8844,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y32" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9170,34 +9126,30 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -11124,34 +11076,30 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11408,34 +11356,30 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11932,34 +11876,30 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12216,34 +12156,30 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12500,34 +12436,30 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12784,34 +12716,30 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -13068,34 +12996,30 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -13352,34 +13276,30 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -13876,34 +13796,30 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14160,34 +14076,30 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -15992,34 +15904,30 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
